--- a/data/roon_database.xlsx
+++ b/data/roon_database.xlsx
@@ -1,54 +1,70 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="products" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="users" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="branch_groups" sheetId="3" state="visible" r:id="rId3"/>
-    <sheet name="area_master" sheetId="4" state="visible" r:id="rId4"/>
-    <sheet name="item_categories" sheetId="5" state="visible" r:id="rId5"/>
-    <sheet name="sales_channels" sheetId="6" state="visible" r:id="rId6"/>
-    <sheet name="roles" sheetId="7" state="visible" r:id="rId7"/>
-    <sheet name="branch_daily_reports" sheetId="8" state="visible" r:id="rId8"/>
-    <sheet name="branch_front_sales_packaging" sheetId="9" state="visible" r:id="rId9"/>
-    <sheet name="branch_drink_sales_detail" sheetId="10" state="visible" r:id="rId10"/>
-    <sheet name="branch_material_balance" sheetId="11" state="visible" r:id="rId11"/>
-    <sheet name="branch_packaging_balance" sheetId="12" state="visible" r:id="rId12"/>
-    <sheet name="delivery_packaging_sales" sheetId="13" state="visible" r:id="rId13"/>
-    <sheet name="branch_other_stock_balance" sheetId="14" state="visible" r:id="rId14"/>
-    <sheet name="branch_special_remark" sheetId="15" state="visible" r:id="rId15"/>
-    <sheet name="branch_sales_recheck" sheetId="16" state="visible" r:id="rId16"/>
-    <sheet name="audit_sessions" sheetId="17" state="visible" r:id="rId17"/>
-    <sheet name="audit_packaging_balance" sheetId="18" state="visible" r:id="rId18"/>
-    <sheet name="audit_packaging_diff" sheetId="19" state="visible" r:id="rId19"/>
-    <sheet name="true_stock_balance" sheetId="20" state="visible" r:id="rId20"/>
-    <sheet name="daily_stock_usage" sheetId="21" state="visible" r:id="rId21"/>
-    <sheet name="daily_packaging_cost" sheetId="22" state="visible" r:id="rId22"/>
-    <sheet name="purchase_orders" sheetId="23" state="visible" r:id="rId23"/>
-    <sheet name="purchase_order_items" sheetId="24" state="visible" r:id="rId24"/>
-    <sheet name="stock_in_to_branch" sheetId="25" state="visible" r:id="rId25"/>
-    <sheet name="production_material_used" sheetId="26" state="visible" r:id="rId26"/>
-    <sheet name="employees" sheetId="27" state="visible" r:id="rId27"/>
-    <sheet name="payroll_periods" sheetId="28" state="visible" r:id="rId28"/>
-    <sheet name="payroll_records" sheetId="29" state="visible" r:id="rId29"/>
-    <sheet name="bank_transactions" sheetId="30" state="visible" r:id="rId30"/>
-    <sheet name="bank_accounts" sheetId="31" state="visible" r:id="rId31"/>
-    <sheet name="branch_expenses" sheetId="32" state="visible" r:id="rId32"/>
-    <sheet name="marketing_daily_sales" sheetId="33" state="visible" r:id="rId33"/>
-    <sheet name="daily_sales_accounting" sheetId="34" state="visible" r:id="rId34"/>
-    <sheet name="sales_reconcile" sheetId="35" state="visible" r:id="rId35"/>
-    <sheet name="department_passwords" sheetId="36" state="visible" r:id="rId36"/>
-    <sheet name="branches" sheetId="37" state="visible" r:id="rId37"/>
-    <sheet name="items" sheetId="38" state="visible" r:id="rId38"/>
-    <sheet name="late_deduction_rules" sheetId="39" state="visible" r:id="rId39"/>
-    <sheet name="production_batches" sheetId="40" state="visible" r:id="rId40"/>
-    <sheet name="stock_movements" sheetId="41" state="visible" r:id="rId41"/>
-    <sheet name="marketing_daily_sales_items" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="products" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="users" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_groups" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="area_master" sheetId="4" state="visible" r:id="rId4"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="item_categories" sheetId="5" state="visible" r:id="rId5"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sales_channels" sheetId="6" state="visible" r:id="rId6"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="roles" sheetId="7" state="visible" r:id="rId7"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_daily_reports" sheetId="8" state="visible" r:id="rId8"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_front_sales_packaging" sheetId="9" state="visible" r:id="rId9"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_drink_sales_detail" sheetId="10" state="visible" r:id="rId10"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_material_balance" sheetId="11" state="visible" r:id="rId11"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_packaging_balance" sheetId="12" state="visible" r:id="rId12"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="delivery_packaging_sales" sheetId="13" state="visible" r:id="rId13"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_other_stock_balance" sheetId="14" state="visible" r:id="rId14"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_special_remark" sheetId="15" state="visible" r:id="rId15"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_sales_recheck" sheetId="16" state="visible" r:id="rId16"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_sessions" sheetId="17" state="visible" r:id="rId17"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_packaging_balance" sheetId="18" state="visible" r:id="rId18"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_packaging_diff" sheetId="19" state="visible" r:id="rId19"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="true_stock_balance" sheetId="20" state="visible" r:id="rId20"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_stock_usage" sheetId="21" state="visible" r:id="rId21"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_packaging_cost" sheetId="22" state="visible" r:id="rId22"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="purchase_orders" sheetId="23" state="visible" r:id="rId23"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="purchase_order_items" sheetId="24" state="visible" r:id="rId24"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stock_in_to_branch" sheetId="25" state="visible" r:id="rId25"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="production_material_used" sheetId="26" state="visible" r:id="rId26"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="employees" sheetId="27" state="visible" r:id="rId27"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="payroll_periods" sheetId="28" state="visible" r:id="rId28"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="payroll_records" sheetId="29" state="visible" r:id="rId29"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bank_transactions" sheetId="30" state="visible" r:id="rId30"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="bank_accounts" sheetId="31" state="visible" r:id="rId31"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_expenses" sheetId="32" state="visible" r:id="rId32"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="marketing_daily_sales" sheetId="33" state="visible" r:id="rId33"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="daily_sales_accounting" sheetId="34" state="visible" r:id="rId34"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="sales_reconcile" sheetId="35" state="visible" r:id="rId35"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="department_passwords" sheetId="36" state="visible" r:id="rId36"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branches" sheetId="37" state="visible" r:id="rId37"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="items" sheetId="38" state="visible" r:id="rId38"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="production_batches" sheetId="39" state="visible" r:id="rId39"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="stock_movements" sheetId="40" state="visible" r:id="rId40"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="late_deduction_rules" sheetId="41" state="visible" r:id="rId41"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="marketing_daily_sales_items" sheetId="42" state="visible" r:id="rId42"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_login" sheetId="43" state="visible" r:id="rId43"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="coupons" sheetId="44" state="visible" r:id="rId44"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_sales" sheetId="45" state="visible" r:id="rId45"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_sales_coupons" sheetId="46" state="visible" r:id="rId46"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_sales_slips" sheetId="47" state="visible" r:id="rId47"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_sales_delivery" sheetId="48" state="visible" r:id="rId48"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="branch_stock_daily" sheetId="49" state="visible" r:id="rId49"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="audit_stock_balance" sheetId="50" state="visible" r:id="rId50"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="material_daily" sheetId="51" state="visible" r:id="rId51"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="material_cost" sheetId="52" state="visible" r:id="rId52"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="petty_cash_funds" sheetId="53" state="visible" r:id="rId53"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="petty_cash_transactions" sheetId="54" state="visible" r:id="rId54"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="petty_cash_requests" sheetId="55" state="visible" r:id="rId55"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="petty_cash_attachments" sheetId="56" state="visible" r:id="rId56"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="assets" sheetId="57" state="visible" r:id="rId57"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="asset_repairs" sheetId="58" state="visible" r:id="rId58"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -5504,43 +5520,119 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G1"/>
+  <dimension ref="A1:H3"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>rule_id</t>
+          <t>batch_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>daily_wage</t>
+          <t>production_date</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>working_hours</t>
+          <t>finished_flour_big_bag</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>hourly_wage</t>
+          <t>finished_flour_small_bag</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>minute_wage</t>
+          <t>ingredient_mix_big_bag</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>late_minutes</t>
+          <t>ingredient_mix_small_bag</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>deduction_amount</t>
+          <t>produced_by</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>remark</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>BATCH001</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>PROD_STAFF</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>ทดสอบ Batch</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>BATCH002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C3" t="n">
+        <v>120</v>
+      </c>
+      <c r="D3" t="n">
+        <v>50</v>
+      </c>
+      <c r="E3" t="n">
+        <v>120</v>
+      </c>
+      <c r="F3" t="n">
+        <v>50</v>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>ประธาน</t>
         </is>
       </c>
     </row>
@@ -5637,46 +5729,66 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H3"/>
+  <dimension ref="A1:L17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>batch_id</t>
+          <t>stock_movement_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>production_date</t>
+          <t>movement_date</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>finished_flour_big_bag</t>
+          <t>item_id</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>finished_flour_small_bag</t>
+          <t>branch_id</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>ingredient_mix_big_bag</t>
+          <t>movement_type</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>ingredient_mix_small_bag</t>
+          <t>qty_in</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>produced_by</t>
+          <t>qty_out</t>
         </is>
       </c>
       <c r="H1" t="inlineStr">
+        <is>
+          <t>unit_cost</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
+          <t>total_value</t>
+        </is>
+      </c>
+      <c r="J1" t="inlineStr">
+        <is>
+          <t>reference_type</t>
+        </is>
+      </c>
+      <c r="K1" t="inlineStr">
+        <is>
+          <t>reference_id</t>
+        </is>
+      </c>
+      <c r="L1" t="inlineStr">
         <is>
           <t>remark</t>
         </is>
@@ -5685,7 +5797,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>BATCH001</t>
+          <t>MV001</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -5695,61 +5807,944 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>5</t>
+          <t>ITM001</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10</t>
+          <t>CENTRAL</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
         <is>
-          <t>3</t>
+          <t>purchase_in</t>
         </is>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>8</t>
+          <t>20</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>PROD_STAFF</t>
+          <t>0</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>ทดสอบ Batch</t>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>400</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>purchase_order</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>PO001</t>
         </is>
       </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
+          <t>MV002</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>ITM002</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>purchase_in</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H3" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>purchase_order</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>PO001</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>MV003</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>ITM001</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>BR001</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>transfer_in</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J4" t="inlineStr">
+        <is>
+          <t>stock_in_to_branch</t>
+        </is>
+      </c>
+      <c r="K4" t="inlineStr">
+        <is>
+          <t>SI001</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>MV004</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>ITM001</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>transfer_out</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr">
+        <is>
+          <t>200</t>
+        </is>
+      </c>
+      <c r="J5" t="inlineStr">
+        <is>
+          <t>stock_in_to_branch</t>
+        </is>
+      </c>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>SI001</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>MV005</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>ITM003</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>BR001</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>transfer_in</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J6" t="inlineStr">
+        <is>
+          <t>stock_in_to_branch</t>
+        </is>
+      </c>
+      <c r="K6" t="inlineStr">
+        <is>
+          <t>SI002</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>MV006</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>ITM003</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>transfer_out</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="H7" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="I7" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="J7" t="inlineStr">
+        <is>
+          <t>stock_in_to_branch</t>
+        </is>
+      </c>
+      <c r="K7" t="inlineStr">
+        <is>
+          <t>SI002</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>MV007</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>ITM001</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>used</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="H8" t="inlineStr">
+        <is>
+          <t>20</t>
+        </is>
+      </c>
+      <c r="I8" t="inlineStr">
+        <is>
+          <t>300</t>
+        </is>
+      </c>
+      <c r="J8" t="inlineStr">
+        <is>
+          <t>production_batch</t>
+        </is>
+      </c>
+      <c r="K8" t="inlineStr">
+        <is>
+          <t>BATCH001</t>
+        </is>
+      </c>
+      <c r="L8" t="inlineStr">
+        <is>
+          <t>ผลิต Batch BATCH001</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>MV008</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>ITM002</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>used</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="H9" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="I9" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="J9" t="inlineStr">
+        <is>
+          <t>production_batch</t>
+        </is>
+      </c>
+      <c r="K9" t="inlineStr">
+        <is>
+          <t>BATCH001</t>
+        </is>
+      </c>
+      <c r="L9" t="inlineStr">
+        <is>
+          <t>ผลิต Batch BATCH001</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>MV009</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>FINISHED_FLOUR_BIG</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>production_in</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J10" t="inlineStr">
+        <is>
+          <t>production_batch</t>
+        </is>
+      </c>
+      <c r="K10" t="inlineStr">
+        <is>
+          <t>BATCH001</t>
+        </is>
+      </c>
+      <c r="L10" t="inlineStr">
+        <is>
+          <t>แป้งสำเร็จรูปถุงใหญ่</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>MV010</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>FINISHED_FLOUR_SMALL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>production_in</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>production_batch</t>
+        </is>
+      </c>
+      <c r="K11" t="inlineStr">
+        <is>
+          <t>BATCH001</t>
+        </is>
+      </c>
+      <c r="L11" t="inlineStr">
+        <is>
+          <t>แป้งสำเร็จรูปถุงเล็ก</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>MV011</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>INGREDIENT_MIX_BIG</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>production_in</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J12" t="inlineStr">
+        <is>
+          <t>production_batch</t>
+        </is>
+      </c>
+      <c r="K12" t="inlineStr">
+        <is>
+          <t>BATCH001</t>
+        </is>
+      </c>
+      <c r="L12" t="inlineStr">
+        <is>
+          <t>ส่วนผสมถุงใหญ่</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>MV012</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>2025-06-01</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>INGREDIENT_MIX_SMALL</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>production_in</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J13" t="inlineStr">
+        <is>
+          <t>production_batch</t>
+        </is>
+      </c>
+      <c r="K13" t="inlineStr">
+        <is>
+          <t>BATCH001</t>
+        </is>
+      </c>
+      <c r="L13" t="inlineStr">
+        <is>
+          <t>ส่วนผสมถุงเล็ก</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>MV013</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>FINISHED_FLOUR_BIG</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>production_in</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>production_batch</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
           <t>BATCH002</t>
         </is>
       </c>
-      <c r="B3" t="inlineStr">
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>แป้งสำเร็จรูปถุงใหญ่</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>MV014</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
         <is>
           <t>2026-06-12</t>
         </is>
       </c>
-      <c r="C3" t="n">
-        <v>120</v>
-      </c>
-      <c r="D3" t="n">
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>FINISHED_FLOUR_SMALL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>production_in</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>50</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>production_batch</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>BATCH002</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>แป้งสำเร็จรูปถุงเล็ก</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>MV015</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>INGREDIENT_MIX_BIG</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>production_in</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>120</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>production_batch</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>BATCH002</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>ส่วนผสมถุงใหญ่</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>MV016</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>2026-06-12</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>INGREDIENT_MIX_SMALL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>CENTRAL</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>production_in</t>
+        </is>
+      </c>
+      <c r="F17" t="n">
         <v>50</v>
       </c>
-      <c r="E3" t="n">
-        <v>120</v>
-      </c>
-      <c r="F3" t="n">
-        <v>50</v>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>ประธาน</t>
+      <c r="G17" t="n">
+        <v>0</v>
+      </c>
+      <c r="H17" t="n">
+        <v>0</v>
+      </c>
+      <c r="I17" t="n">
+        <v>0</v>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>production_batch</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>BATCH002</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>ส่วนผสมถุงเล็ก</t>
         </is>
       </c>
     </row>
@@ -5764,1022 +6759,43 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:L17"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>stock_movement_id</t>
+          <t>rule_id</t>
         </is>
       </c>
       <c r="B1" t="inlineStr">
         <is>
-          <t>movement_date</t>
+          <t>daily_wage</t>
         </is>
       </c>
       <c r="C1" t="inlineStr">
         <is>
-          <t>item_id</t>
+          <t>working_hours</t>
         </is>
       </c>
       <c r="D1" t="inlineStr">
         <is>
-          <t>branch_id</t>
+          <t>hourly_wage</t>
         </is>
       </c>
       <c r="E1" t="inlineStr">
         <is>
-          <t>movement_type</t>
+          <t>minute_wage</t>
         </is>
       </c>
       <c r="F1" t="inlineStr">
         <is>
-          <t>qty_in</t>
+          <t>late_minutes</t>
         </is>
       </c>
       <c r="G1" t="inlineStr">
         <is>
-          <t>qty_out</t>
-        </is>
-      </c>
-      <c r="H1" t="inlineStr">
-        <is>
-          <t>unit_cost</t>
-        </is>
-      </c>
-      <c r="I1" t="inlineStr">
-        <is>
-          <t>total_value</t>
-        </is>
-      </c>
-      <c r="J1" t="inlineStr">
-        <is>
-          <t>reference_type</t>
-        </is>
-      </c>
-      <c r="K1" t="inlineStr">
-        <is>
-          <t>reference_id</t>
-        </is>
-      </c>
-      <c r="L1" t="inlineStr">
-        <is>
-          <t>remark</t>
-        </is>
-      </c>
-    </row>
-    <row r="2">
-      <c r="A2" t="inlineStr">
-        <is>
-          <t>MV001</t>
-        </is>
-      </c>
-      <c r="B2" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>ITM001</t>
-        </is>
-      </c>
-      <c r="D2" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E2" t="inlineStr">
-        <is>
-          <t>purchase_in</t>
-        </is>
-      </c>
-      <c r="F2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>400</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>purchase_order</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>PO001</t>
-        </is>
-      </c>
-    </row>
-    <row r="3">
-      <c r="A3" t="inlineStr">
-        <is>
-          <t>MV002</t>
-        </is>
-      </c>
-      <c r="B3" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>ITM002</t>
-        </is>
-      </c>
-      <c r="D3" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E3" t="inlineStr">
-        <is>
-          <t>purchase_in</t>
-        </is>
-      </c>
-      <c r="F3" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H3" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>150</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>purchase_order</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>PO001</t>
-        </is>
-      </c>
-    </row>
-    <row r="4">
-      <c r="A4" t="inlineStr">
-        <is>
-          <t>MV003</t>
-        </is>
-      </c>
-      <c r="B4" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="C4" t="inlineStr">
-        <is>
-          <t>ITM001</t>
-        </is>
-      </c>
-      <c r="D4" t="inlineStr">
-        <is>
-          <t>BR001</t>
-        </is>
-      </c>
-      <c r="E4" t="inlineStr">
-        <is>
-          <t>transfer_in</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H4" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I4" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J4" t="inlineStr">
-        <is>
-          <t>stock_in_to_branch</t>
-        </is>
-      </c>
-      <c r="K4" t="inlineStr">
-        <is>
-          <t>SI001</t>
-        </is>
-      </c>
-    </row>
-    <row r="5">
-      <c r="A5" t="inlineStr">
-        <is>
-          <t>MV004</t>
-        </is>
-      </c>
-      <c r="B5" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="C5" t="inlineStr">
-        <is>
-          <t>ITM001</t>
-        </is>
-      </c>
-      <c r="D5" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E5" t="inlineStr">
-        <is>
-          <t>transfer_out</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G5" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="H5" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I5" t="inlineStr">
-        <is>
-          <t>200</t>
-        </is>
-      </c>
-      <c r="J5" t="inlineStr">
-        <is>
-          <t>stock_in_to_branch</t>
-        </is>
-      </c>
-      <c r="K5" t="inlineStr">
-        <is>
-          <t>SI001</t>
-        </is>
-      </c>
-    </row>
-    <row r="6">
-      <c r="A6" t="inlineStr">
-        <is>
-          <t>MV005</t>
-        </is>
-      </c>
-      <c r="B6" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="C6" t="inlineStr">
-        <is>
-          <t>ITM003</t>
-        </is>
-      </c>
-      <c r="D6" t="inlineStr">
-        <is>
-          <t>BR001</t>
-        </is>
-      </c>
-      <c r="E6" t="inlineStr">
-        <is>
-          <t>transfer_in</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="G6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H6" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I6" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J6" t="inlineStr">
-        <is>
-          <t>stock_in_to_branch</t>
-        </is>
-      </c>
-      <c r="K6" t="inlineStr">
-        <is>
-          <t>SI002</t>
-        </is>
-      </c>
-    </row>
-    <row r="7">
-      <c r="A7" t="inlineStr">
-        <is>
-          <t>MV006</t>
-        </is>
-      </c>
-      <c r="B7" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="C7" t="inlineStr">
-        <is>
-          <t>ITM003</t>
-        </is>
-      </c>
-      <c r="D7" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E7" t="inlineStr">
-        <is>
-          <t>transfer_out</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G7" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="H7" t="inlineStr">
-        <is>
-          <t>2</t>
-        </is>
-      </c>
-      <c r="I7" t="inlineStr">
-        <is>
-          <t>100</t>
-        </is>
-      </c>
-      <c r="J7" t="inlineStr">
-        <is>
-          <t>stock_in_to_branch</t>
-        </is>
-      </c>
-      <c r="K7" t="inlineStr">
-        <is>
-          <t>SI002</t>
-        </is>
-      </c>
-    </row>
-    <row r="8">
-      <c r="A8" t="inlineStr">
-        <is>
-          <t>MV007</t>
-        </is>
-      </c>
-      <c r="B8" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="C8" t="inlineStr">
-        <is>
-          <t>ITM001</t>
-        </is>
-      </c>
-      <c r="D8" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E8" t="inlineStr">
-        <is>
-          <t>used</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G8" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="H8" t="inlineStr">
-        <is>
-          <t>20</t>
-        </is>
-      </c>
-      <c r="I8" t="inlineStr">
-        <is>
-          <t>300</t>
-        </is>
-      </c>
-      <c r="J8" t="inlineStr">
-        <is>
-          <t>production_batch</t>
-        </is>
-      </c>
-      <c r="K8" t="inlineStr">
-        <is>
-          <t>BATCH001</t>
-        </is>
-      </c>
-      <c r="L8" t="inlineStr">
-        <is>
-          <t>ผลิต Batch BATCH001</t>
-        </is>
-      </c>
-    </row>
-    <row r="9">
-      <c r="A9" t="inlineStr">
-        <is>
-          <t>MV008</t>
-        </is>
-      </c>
-      <c r="B9" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="C9" t="inlineStr">
-        <is>
-          <t>ITM002</t>
-        </is>
-      </c>
-      <c r="D9" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E9" t="inlineStr">
-        <is>
-          <t>used</t>
-        </is>
-      </c>
-      <c r="F9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="G9" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="H9" t="inlineStr">
-        <is>
-          <t>30</t>
-        </is>
-      </c>
-      <c r="I9" t="inlineStr">
-        <is>
-          <t>90</t>
-        </is>
-      </c>
-      <c r="J9" t="inlineStr">
-        <is>
-          <t>production_batch</t>
-        </is>
-      </c>
-      <c r="K9" t="inlineStr">
-        <is>
-          <t>BATCH001</t>
-        </is>
-      </c>
-      <c r="L9" t="inlineStr">
-        <is>
-          <t>ผลิต Batch BATCH001</t>
-        </is>
-      </c>
-    </row>
-    <row r="10">
-      <c r="A10" t="inlineStr">
-        <is>
-          <t>MV009</t>
-        </is>
-      </c>
-      <c r="B10" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="C10" t="inlineStr">
-        <is>
-          <t>FINISHED_FLOUR_BIG</t>
-        </is>
-      </c>
-      <c r="D10" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E10" t="inlineStr">
-        <is>
-          <t>production_in</t>
-        </is>
-      </c>
-      <c r="F10" t="inlineStr">
-        <is>
-          <t>5</t>
-        </is>
-      </c>
-      <c r="G10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J10" t="inlineStr">
-        <is>
-          <t>production_batch</t>
-        </is>
-      </c>
-      <c r="K10" t="inlineStr">
-        <is>
-          <t>BATCH001</t>
-        </is>
-      </c>
-      <c r="L10" t="inlineStr">
-        <is>
-          <t>แป้งสำเร็จรูปถุงใหญ่</t>
-        </is>
-      </c>
-    </row>
-    <row r="11">
-      <c r="A11" t="inlineStr">
-        <is>
-          <t>MV010</t>
-        </is>
-      </c>
-      <c r="B11" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="C11" t="inlineStr">
-        <is>
-          <t>FINISHED_FLOUR_SMALL</t>
-        </is>
-      </c>
-      <c r="D11" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E11" t="inlineStr">
-        <is>
-          <t>production_in</t>
-        </is>
-      </c>
-      <c r="F11" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="G11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J11" t="inlineStr">
-        <is>
-          <t>production_batch</t>
-        </is>
-      </c>
-      <c r="K11" t="inlineStr">
-        <is>
-          <t>BATCH001</t>
-        </is>
-      </c>
-      <c r="L11" t="inlineStr">
-        <is>
-          <t>แป้งสำเร็จรูปถุงเล็ก</t>
-        </is>
-      </c>
-    </row>
-    <row r="12">
-      <c r="A12" t="inlineStr">
-        <is>
-          <t>MV011</t>
-        </is>
-      </c>
-      <c r="B12" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="C12" t="inlineStr">
-        <is>
-          <t>INGREDIENT_MIX_BIG</t>
-        </is>
-      </c>
-      <c r="D12" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E12" t="inlineStr">
-        <is>
-          <t>production_in</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>3</t>
-        </is>
-      </c>
-      <c r="G12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J12" t="inlineStr">
-        <is>
-          <t>production_batch</t>
-        </is>
-      </c>
-      <c r="K12" t="inlineStr">
-        <is>
-          <t>BATCH001</t>
-        </is>
-      </c>
-      <c r="L12" t="inlineStr">
-        <is>
-          <t>ส่วนผสมถุงใหญ่</t>
-        </is>
-      </c>
-    </row>
-    <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>MV012</t>
-        </is>
-      </c>
-      <c r="B13" t="inlineStr">
-        <is>
-          <t>2025-06-01</t>
-        </is>
-      </c>
-      <c r="C13" t="inlineStr">
-        <is>
-          <t>INGREDIENT_MIX_SMALL</t>
-        </is>
-      </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>production_in</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>8</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J13" t="inlineStr">
-        <is>
-          <t>production_batch</t>
-        </is>
-      </c>
-      <c r="K13" t="inlineStr">
-        <is>
-          <t>BATCH001</t>
-        </is>
-      </c>
-      <c r="L13" t="inlineStr">
-        <is>
-          <t>ส่วนผสมถุงเล็ก</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>MV013</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>FINISHED_FLOUR_BIG</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>production_in</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>production_batch</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>BATCH002</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>แป้งสำเร็จรูปถุงใหญ่</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>MV014</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>FINISHED_FLOUR_SMALL</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>production_in</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>50</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>production_batch</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>BATCH002</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>แป้งสำเร็จรูปถุงเล็ก</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>MV015</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>INGREDIENT_MIX_BIG</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>production_in</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>120</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>production_batch</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>BATCH002</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>ส่วนผสมถุงใหญ่</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>MV016</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>2026-06-12</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>INGREDIENT_MIX_SMALL</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>CENTRAL</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>production_in</t>
-        </is>
-      </c>
-      <c r="F17" t="n">
-        <v>50</v>
-      </c>
-      <c r="G17" t="n">
-        <v>0</v>
-      </c>
-      <c r="H17" t="n">
-        <v>0</v>
-      </c>
-      <c r="I17" t="n">
-        <v>0</v>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>production_batch</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>BATCH002</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>ส่วนผสมถุงเล็ก</t>
+          <t>deduction_amount</t>
         </is>
       </c>
     </row>
@@ -6834,6 +6850,97 @@
 </worksheet>
 </file>
 
+<file path=xl/worksheets/sheet43.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet44.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet45.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet46.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet47.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet48.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet49.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <sheetPr>
@@ -6997,6 +7104,123 @@
       </c>
     </row>
   </sheetData>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet50.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet51.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet52.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet53.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet54.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet55.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet56.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet57.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
+  <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet58.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+  <sheetPr>
+    <outlinePr summaryBelow="1" summaryRight="1"/>
+    <pageSetUpPr/>
+  </sheetPr>
+  <dimension ref="A1:A1"/>
+  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
+  <sheetData/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
